--- a/dist/downloads/model-documents/openbmb-agentcpm-gui.xlsx
+++ b/dist/downloads/model-documents/openbmb-agentcpm-gui.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="算子表" sheetId="1" r:id="R0c16ca1ec2b94521"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型参数" sheetId="2" r:id="Rcf64c08c83644474"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="算子表" sheetId="1" r:id="R95457ceabd6145ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型参数" sheetId="2" r:id="R06908ae0492745c2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1061,7 +1061,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD6" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" hidden="0" customHeight="1">
@@ -2257,7 +2257,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD19" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="24" hidden="0" customHeight="1">
@@ -3453,7 +3453,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD32" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="24" hidden="0" customHeight="1">
@@ -4649,7 +4649,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD45" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="24" hidden="0" customHeight="1">
@@ -5845,7 +5845,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD58" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="24" hidden="0" customHeight="1">
@@ -7041,7 +7041,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD71" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="24" hidden="0" customHeight="1">
@@ -8237,7 +8237,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD84" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="24" hidden="0" customHeight="1">
@@ -9433,7 +9433,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD97" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="24" hidden="0" customHeight="1">
@@ -10629,7 +10629,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD110" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="24" hidden="0" customHeight="1">
@@ -11825,7 +11825,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD123" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="24" hidden="0" customHeight="1">
@@ -13021,7 +13021,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD136" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="24" hidden="0" customHeight="1">
@@ -14217,7 +14217,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD149" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="24" hidden="0" customHeight="1">
@@ -15413,7 +15413,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD162" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="24" hidden="0" customHeight="1">
@@ -16609,7 +16609,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD175" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="24" hidden="0" customHeight="1">
@@ -17805,7 +17805,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD188" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="24" hidden="0" customHeight="1">
@@ -19001,7 +19001,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD201" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="24" hidden="0" customHeight="1">
@@ -20197,7 +20197,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD214" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="24" hidden="0" customHeight="1">
@@ -21393,7 +21393,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD227" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="24" hidden="0" customHeight="1">
@@ -22589,7 +22589,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD240" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="241" ht="24" hidden="0" customHeight="1">
@@ -23785,7 +23785,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD253" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="254" ht="24" hidden="0" customHeight="1">
@@ -24981,7 +24981,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD266" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="267" ht="24" hidden="0" customHeight="1">
@@ -26177,7 +26177,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD279" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="280" ht="24" hidden="0" customHeight="1">
@@ -27373,7 +27373,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD292" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="293" ht="24" hidden="0" customHeight="1">
@@ -28569,7 +28569,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD305" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="306" ht="24" hidden="0" customHeight="1">
@@ -29765,7 +29765,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD318" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="319" ht="24" hidden="0" customHeight="1">
@@ -30961,7 +30961,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD331" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="332" ht="24" hidden="0" customHeight="1">
@@ -32157,7 +32157,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD344" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="345" ht="24" hidden="0" customHeight="1">
@@ -33353,7 +33353,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD357" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="358" ht="24" hidden="0" customHeight="1">
@@ -34112,10 +34112,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G366" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H366" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I366" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34178,7 +34178,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC366" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD366" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -34204,10 +34204,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G367" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H367" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I367" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34270,7 +34270,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC367" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD367" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -34296,10 +34296,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G368" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H368" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I368" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34362,7 +34362,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC368" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD368" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -34388,10 +34388,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G369" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H369" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I369" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34454,7 +34454,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC369" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD369" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -34465,25 +34465,25 @@
         <x:v>vision_config/layer_0</x:v>
       </x:c>
       <x:c r="B370" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C370" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D370" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E370" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F370" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G370" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H370" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I370" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34546,10 +34546,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC370" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD370" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="371" ht="24" hidden="0" customHeight="1">
@@ -34572,10 +34572,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G371" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H371" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I371" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34638,7 +34638,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC371" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD371" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -34664,10 +34664,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G372" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H372" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I372" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34730,7 +34730,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC372" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD372" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -34756,10 +34756,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G373" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H373" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I373" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34822,7 +34822,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC373" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD373" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -34848,10 +34848,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G374" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H374" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I374" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34914,7 +34914,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC374" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD374" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -34940,10 +34940,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G375" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H375" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I375" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35006,7 +35006,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC375" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD375" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -35032,10 +35032,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G376" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H376" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I376" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35098,7 +35098,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC376" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD376" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -35124,10 +35124,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G377" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H377" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I377" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35190,7 +35190,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC377" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD377" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -35216,10 +35216,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G378" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H378" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I378" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35282,7 +35282,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC378" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD378" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -35308,10 +35308,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G379" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H379" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I379" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35374,7 +35374,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC379" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD379" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -35400,10 +35400,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G380" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H380" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I380" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35466,7 +35466,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC380" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD380" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -35492,10 +35492,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G381" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H381" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I381" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35558,7 +35558,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC381" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD381" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -35584,10 +35584,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G382" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H382" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I382" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35650,7 +35650,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC382" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD382" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -35661,25 +35661,25 @@
         <x:v>vision_config/layer_1</x:v>
       </x:c>
       <x:c r="B383" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C383" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D383" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E383" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F383" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G383" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H383" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I383" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35742,10 +35742,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC383" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD383" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="384" ht="24" hidden="0" customHeight="1">
@@ -35768,10 +35768,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G384" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H384" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I384" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35834,7 +35834,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC384" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD384" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -35860,10 +35860,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G385" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H385" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I385" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35926,7 +35926,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC385" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD385" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -35952,10 +35952,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G386" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H386" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I386" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36018,7 +36018,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC386" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD386" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -36044,10 +36044,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G387" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H387" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I387" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36110,7 +36110,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC387" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD387" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -36136,10 +36136,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G388" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H388" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I388" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36202,7 +36202,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC388" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD388" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -36228,10 +36228,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G389" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H389" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I389" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36294,7 +36294,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC389" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD389" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -36320,10 +36320,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G390" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H390" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I390" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36386,7 +36386,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC390" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD390" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -36412,10 +36412,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G391" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H391" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I391" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36478,7 +36478,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC391" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD391" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -36504,10 +36504,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G392" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H392" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I392" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36570,7 +36570,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC392" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD392" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -36596,10 +36596,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G393" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H393" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I393" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36662,7 +36662,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC393" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD393" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -36688,10 +36688,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G394" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H394" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I394" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36754,7 +36754,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC394" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD394" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -36780,10 +36780,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G395" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H395" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I395" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36846,7 +36846,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC395" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD395" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -36857,25 +36857,25 @@
         <x:v>vision_config/layer_2</x:v>
       </x:c>
       <x:c r="B396" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C396" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D396" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E396" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F396" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G396" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H396" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I396" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36938,10 +36938,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC396" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD396" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="397" ht="24" hidden="0" customHeight="1">
@@ -36964,10 +36964,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G397" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H397" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I397" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37030,7 +37030,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC397" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD397" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -37056,10 +37056,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G398" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H398" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I398" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37122,7 +37122,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC398" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD398" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -37148,10 +37148,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G399" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H399" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I399" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37214,7 +37214,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC399" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD399" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -37240,10 +37240,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G400" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H400" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I400" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37306,7 +37306,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC400" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD400" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -37332,10 +37332,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G401" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H401" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I401" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37398,7 +37398,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC401" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD401" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -37424,10 +37424,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G402" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H402" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I402" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37490,7 +37490,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC402" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD402" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -37516,10 +37516,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G403" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H403" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I403" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37582,7 +37582,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC403" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD403" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -37608,10 +37608,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G404" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H404" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I404" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37674,7 +37674,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC404" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD404" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -37700,10 +37700,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G405" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H405" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I405" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37766,7 +37766,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC405" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD405" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -37792,10 +37792,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G406" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H406" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I406" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37858,7 +37858,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC406" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD406" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -37884,10 +37884,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G407" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H407" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I407" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37950,7 +37950,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC407" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD407" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -37976,10 +37976,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G408" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H408" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I408" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38042,7 +38042,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC408" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD408" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -38053,25 +38053,25 @@
         <x:v>vision_config/layer_3</x:v>
       </x:c>
       <x:c r="B409" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C409" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D409" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E409" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F409" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G409" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H409" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I409" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38134,10 +38134,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC409" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD409" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="410" ht="24" hidden="0" customHeight="1">
@@ -38160,10 +38160,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G410" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H410" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I410" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38226,7 +38226,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC410" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD410" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -38252,10 +38252,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G411" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H411" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I411" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38318,7 +38318,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC411" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD411" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -38344,10 +38344,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G412" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H412" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I412" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38410,7 +38410,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC412" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD412" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -38436,10 +38436,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G413" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H413" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I413" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38502,7 +38502,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC413" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD413" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -38528,10 +38528,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G414" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H414" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I414" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38594,7 +38594,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC414" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD414" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -38620,10 +38620,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G415" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H415" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I415" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38686,7 +38686,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC415" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD415" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -38712,10 +38712,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G416" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H416" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I416" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38778,7 +38778,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC416" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD416" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -38804,10 +38804,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G417" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H417" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I417" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38870,7 +38870,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC417" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD417" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -38896,10 +38896,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G418" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H418" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I418" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -38962,7 +38962,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC418" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD418" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -38988,10 +38988,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G419" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H419" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I419" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39054,7 +39054,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC419" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD419" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -39080,10 +39080,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G420" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H420" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I420" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39146,7 +39146,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC420" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD420" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -39172,10 +39172,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G421" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H421" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I421" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39238,7 +39238,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC421" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD421" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -39249,25 +39249,25 @@
         <x:v>vision_config/layer_4</x:v>
       </x:c>
       <x:c r="B422" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C422" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D422" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E422" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F422" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G422" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H422" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I422" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39330,10 +39330,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC422" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD422" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="423" ht="24" hidden="0" customHeight="1">
@@ -39356,10 +39356,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G423" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H423" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I423" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39422,7 +39422,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC423" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD423" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -39448,10 +39448,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G424" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H424" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I424" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39514,7 +39514,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC424" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD424" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -39540,10 +39540,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G425" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H425" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I425" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39606,7 +39606,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC425" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD425" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -39632,10 +39632,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G426" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H426" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I426" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39698,7 +39698,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC426" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD426" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -39724,10 +39724,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G427" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H427" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I427" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39790,7 +39790,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC427" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD427" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -39816,10 +39816,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G428" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H428" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I428" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39882,7 +39882,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC428" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD428" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -39908,10 +39908,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G429" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H429" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I429" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -39974,7 +39974,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC429" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD429" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -40000,10 +40000,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G430" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H430" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I430" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40066,7 +40066,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC430" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD430" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -40092,10 +40092,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G431" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H431" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I431" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40158,7 +40158,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC431" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD431" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -40184,10 +40184,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G432" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H432" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I432" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40250,7 +40250,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC432" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD432" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -40276,10 +40276,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G433" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H433" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I433" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40342,7 +40342,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC433" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD433" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -40368,10 +40368,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G434" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H434" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I434" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40434,7 +40434,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC434" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD434" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -40445,25 +40445,25 @@
         <x:v>vision_config/layer_5</x:v>
       </x:c>
       <x:c r="B435" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C435" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D435" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E435" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F435" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G435" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H435" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I435" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40526,10 +40526,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC435" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD435" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="436" ht="24" hidden="0" customHeight="1">
@@ -40552,10 +40552,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G436" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H436" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I436" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40618,7 +40618,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC436" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD436" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -40644,10 +40644,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G437" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H437" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I437" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40710,7 +40710,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC437" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD437" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -40736,10 +40736,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G438" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H438" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I438" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40802,7 +40802,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC438" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD438" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -40828,10 +40828,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G439" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H439" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I439" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40894,7 +40894,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC439" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD439" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -40920,10 +40920,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G440" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H440" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I440" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -40986,7 +40986,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC440" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD440" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -41012,10 +41012,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G441" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H441" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I441" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41078,7 +41078,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC441" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD441" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -41104,10 +41104,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G442" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H442" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I442" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41170,7 +41170,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC442" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD442" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -41196,10 +41196,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G443" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H443" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I443" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41262,7 +41262,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC443" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD443" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -41288,10 +41288,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G444" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H444" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I444" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41354,7 +41354,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC444" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD444" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -41380,10 +41380,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G445" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H445" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I445" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41446,7 +41446,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC445" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD445" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -41472,10 +41472,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G446" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H446" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I446" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41538,7 +41538,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC446" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD446" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -41564,10 +41564,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G447" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H447" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I447" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41630,7 +41630,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC447" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD447" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -41641,25 +41641,25 @@
         <x:v>vision_config/layer_6</x:v>
       </x:c>
       <x:c r="B448" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C448" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D448" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E448" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F448" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G448" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H448" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I448" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41722,10 +41722,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC448" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD448" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="449" ht="24" hidden="0" customHeight="1">
@@ -41748,10 +41748,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G449" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H449" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I449" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41814,7 +41814,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC449" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD449" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -41840,10 +41840,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G450" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H450" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I450" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41906,7 +41906,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC450" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD450" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -41932,10 +41932,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G451" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H451" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I451" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -41998,7 +41998,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC451" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD451" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -42024,10 +42024,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G452" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H452" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I452" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -42090,7 +42090,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC452" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD452" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -42116,10 +42116,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G453" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H453" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I453" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -42182,7 +42182,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC453" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD453" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -42208,10 +42208,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G454" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H454" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I454" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -42274,7 +42274,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC454" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD454" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -42300,10 +42300,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G455" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H455" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I455" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -42366,7 +42366,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC455" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD455" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -42392,10 +42392,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G456" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H456" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I456" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -42458,7 +42458,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC456" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD456" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -42484,10 +42484,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G457" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H457" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I457" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -42550,7 +42550,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC457" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD457" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -42576,10 +42576,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G458" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H458" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I458" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -42642,7 +42642,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC458" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD458" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -42668,10 +42668,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G459" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H459" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I459" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -42734,7 +42734,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC459" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD459" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -42760,10 +42760,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G460" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H460" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I460" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -42826,7 +42826,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC460" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD460" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -42837,25 +42837,25 @@
         <x:v>vision_config/layer_7</x:v>
       </x:c>
       <x:c r="B461" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C461" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D461" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E461" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F461" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G461" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H461" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I461" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -42918,10 +42918,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC461" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD461" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="462" ht="24" hidden="0" customHeight="1">
@@ -42944,10 +42944,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G462" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H462" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I462" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -43010,7 +43010,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC462" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD462" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -43036,10 +43036,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G463" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H463" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I463" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -43102,7 +43102,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC463" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD463" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -43128,10 +43128,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G464" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H464" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I464" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -43194,7 +43194,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC464" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD464" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -43220,10 +43220,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G465" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H465" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I465" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -43286,7 +43286,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC465" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD465" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -43312,10 +43312,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G466" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H466" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I466" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -43378,7 +43378,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC466" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD466" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -43404,10 +43404,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G467" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H467" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I467" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -43470,7 +43470,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC467" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD467" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -43496,10 +43496,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G468" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H468" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I468" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -43562,7 +43562,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC468" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD468" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -43588,10 +43588,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G469" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H469" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I469" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -43654,7 +43654,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC469" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD469" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -43680,10 +43680,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G470" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H470" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I470" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -43746,7 +43746,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC470" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD470" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -43772,10 +43772,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G471" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H471" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I471" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -43838,7 +43838,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC471" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD471" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -43864,10 +43864,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G472" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H472" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I472" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -43930,7 +43930,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC472" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD472" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -43956,10 +43956,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G473" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H473" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I473" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -44022,7 +44022,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC473" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD473" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -44033,25 +44033,25 @@
         <x:v>vision_config/layer_8</x:v>
       </x:c>
       <x:c r="B474" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C474" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D474" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E474" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F474" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G474" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H474" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I474" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -44114,10 +44114,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC474" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD474" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="475" ht="24" hidden="0" customHeight="1">
@@ -44140,10 +44140,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G475" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H475" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I475" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -44206,7 +44206,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC475" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD475" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -44232,10 +44232,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G476" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H476" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I476" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -44298,7 +44298,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC476" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD476" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -44324,10 +44324,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G477" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H477" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I477" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -44390,7 +44390,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC477" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD477" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -44416,10 +44416,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G478" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H478" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I478" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -44482,7 +44482,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC478" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD478" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -44508,10 +44508,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G479" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H479" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I479" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -44574,7 +44574,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC479" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD479" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -44600,10 +44600,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G480" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H480" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I480" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -44666,7 +44666,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC480" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD480" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -44692,10 +44692,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G481" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H481" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I481" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -44758,7 +44758,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC481" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD481" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -44784,10 +44784,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G482" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H482" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I482" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -44850,7 +44850,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC482" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD482" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -44876,10 +44876,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G483" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H483" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I483" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -44942,7 +44942,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC483" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD483" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -44968,10 +44968,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G484" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H484" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I484" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -45034,7 +45034,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC484" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD484" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -45060,10 +45060,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G485" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H485" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I485" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -45126,7 +45126,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC485" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD485" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -45152,10 +45152,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G486" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H486" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I486" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -45218,7 +45218,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC486" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD486" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -45229,25 +45229,25 @@
         <x:v>vision_config/layer_9</x:v>
       </x:c>
       <x:c r="B487" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C487" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D487" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E487" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F487" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G487" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H487" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I487" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -45310,10 +45310,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC487" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD487" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="488" ht="24" hidden="0" customHeight="1">
@@ -45336,10 +45336,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G488" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H488" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I488" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -45402,7 +45402,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC488" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD488" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -45428,10 +45428,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G489" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H489" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I489" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -45494,7 +45494,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC489" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD489" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -45520,10 +45520,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G490" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H490" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I490" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -45586,7 +45586,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC490" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD490" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -45612,10 +45612,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G491" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H491" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I491" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -45678,7 +45678,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC491" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD491" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -45704,10 +45704,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G492" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H492" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I492" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -45770,7 +45770,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC492" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD492" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -45796,10 +45796,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G493" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H493" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I493" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -45862,7 +45862,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC493" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD493" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -45888,10 +45888,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G494" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H494" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I494" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -45954,7 +45954,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC494" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD494" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -45980,10 +45980,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G495" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H495" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I495" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -46046,7 +46046,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC495" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD495" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -46072,10 +46072,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G496" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H496" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I496" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -46138,7 +46138,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC496" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD496" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -46164,10 +46164,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G497" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H497" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I497" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -46230,7 +46230,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC497" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD497" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -46256,10 +46256,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G498" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H498" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I498" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -46322,7 +46322,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC498" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD498" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -46348,10 +46348,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G499" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H499" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I499" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -46414,7 +46414,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC499" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD499" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -46425,25 +46425,25 @@
         <x:v>vision_config/layer_10</x:v>
       </x:c>
       <x:c r="B500" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C500" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D500" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E500" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F500" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G500" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H500" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I500" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -46506,10 +46506,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC500" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD500" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="501" ht="24" hidden="0" customHeight="1">
@@ -46532,10 +46532,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G501" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H501" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I501" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -46598,7 +46598,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC501" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD501" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -46624,10 +46624,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G502" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H502" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I502" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -46690,7 +46690,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC502" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD502" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -46716,10 +46716,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G503" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H503" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I503" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -46782,7 +46782,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC503" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD503" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -46808,10 +46808,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G504" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H504" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I504" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -46874,7 +46874,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC504" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD504" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -46900,10 +46900,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G505" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H505" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I505" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -46966,7 +46966,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC505" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD505" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -46992,10 +46992,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G506" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H506" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I506" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -47058,7 +47058,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC506" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD506" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -47084,10 +47084,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G507" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H507" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I507" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -47150,7 +47150,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC507" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD507" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -47176,10 +47176,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G508" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H508" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I508" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -47242,7 +47242,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC508" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD508" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -47268,10 +47268,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G509" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H509" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I509" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -47334,7 +47334,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC509" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD509" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -47360,10 +47360,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G510" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H510" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I510" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -47426,7 +47426,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC510" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD510" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -47452,10 +47452,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G511" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H511" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I511" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -47518,7 +47518,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC511" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD511" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -47544,10 +47544,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G512" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H512" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I512" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -47610,7 +47610,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC512" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD512" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -47621,25 +47621,25 @@
         <x:v>vision_config/layer_11</x:v>
       </x:c>
       <x:c r="B513" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C513" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D513" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E513" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F513" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G513" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H513" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I513" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -47702,10 +47702,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC513" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD513" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="514" ht="24" hidden="0" customHeight="1">
@@ -47728,10 +47728,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G514" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H514" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I514" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -47794,7 +47794,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC514" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD514" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -47820,10 +47820,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G515" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H515" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I515" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -47886,7 +47886,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC515" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD515" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -47912,10 +47912,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G516" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H516" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I516" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -47978,7 +47978,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC516" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD516" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -48004,10 +48004,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G517" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H517" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I517" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -48070,7 +48070,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC517" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD517" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -48096,10 +48096,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G518" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H518" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I518" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -48162,7 +48162,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC518" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD518" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -48188,10 +48188,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G519" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H519" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I519" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -48254,7 +48254,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC519" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD519" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -48280,10 +48280,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G520" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H520" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I520" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -48346,7 +48346,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC520" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD520" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -48372,10 +48372,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G521" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H521" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I521" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -48438,7 +48438,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC521" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD521" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -48464,10 +48464,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G522" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H522" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I522" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -48530,7 +48530,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC522" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD522" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -48556,10 +48556,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G523" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H523" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I523" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -48622,7 +48622,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC523" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD523" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -48648,10 +48648,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G524" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H524" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I524" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -48714,7 +48714,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC524" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD524" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -48740,10 +48740,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G525" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H525" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I525" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -48806,7 +48806,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC525" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD525" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -48817,25 +48817,25 @@
         <x:v>vision_config/layer_12</x:v>
       </x:c>
       <x:c r="B526" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C526" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D526" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E526" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F526" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G526" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H526" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I526" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -48898,10 +48898,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC526" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD526" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="527" ht="24" hidden="0" customHeight="1">
@@ -48924,10 +48924,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G527" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H527" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I527" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -48990,7 +48990,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC527" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD527" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -49016,10 +49016,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G528" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H528" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I528" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -49082,7 +49082,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC528" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD528" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -49108,10 +49108,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G529" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H529" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I529" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -49174,7 +49174,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC529" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD529" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -49200,10 +49200,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G530" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H530" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I530" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -49266,7 +49266,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC530" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD530" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -49292,10 +49292,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G531" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H531" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I531" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -49358,7 +49358,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC531" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD531" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -49384,10 +49384,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G532" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H532" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I532" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -49450,7 +49450,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC532" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD532" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -49476,10 +49476,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G533" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H533" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I533" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -49542,7 +49542,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC533" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD533" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -49568,10 +49568,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G534" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H534" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I534" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -49634,7 +49634,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC534" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD534" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -49660,10 +49660,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G535" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H535" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I535" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -49726,7 +49726,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC535" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD535" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -49752,10 +49752,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G536" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H536" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I536" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -49818,7 +49818,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC536" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD536" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -49844,10 +49844,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G537" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H537" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I537" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -49910,7 +49910,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC537" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD537" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -49936,10 +49936,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G538" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H538" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I538" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -50002,7 +50002,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC538" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD538" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -50013,25 +50013,25 @@
         <x:v>vision_config/layer_13</x:v>
       </x:c>
       <x:c r="B539" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C539" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D539" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E539" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F539" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G539" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H539" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I539" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -50094,10 +50094,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC539" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD539" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="540" ht="24" hidden="0" customHeight="1">
@@ -50120,10 +50120,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G540" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H540" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I540" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -50186,7 +50186,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC540" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD540" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -50212,10 +50212,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G541" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H541" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I541" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -50278,7 +50278,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC541" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD541" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -50304,10 +50304,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G542" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H542" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I542" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -50370,7 +50370,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC542" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD542" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -50396,10 +50396,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G543" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H543" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I543" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -50462,7 +50462,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC543" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD543" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -50488,10 +50488,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G544" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H544" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I544" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -50554,7 +50554,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC544" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD544" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -50580,10 +50580,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G545" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H545" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I545" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -50646,7 +50646,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC545" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD545" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -50672,10 +50672,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G546" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H546" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I546" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -50738,7 +50738,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC546" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD546" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -50764,10 +50764,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G547" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H547" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I547" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -50830,7 +50830,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC547" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD547" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -50856,10 +50856,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G548" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H548" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I548" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -50922,7 +50922,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC548" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD548" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -50948,10 +50948,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G549" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H549" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I549" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -51014,7 +51014,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC549" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD549" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -51040,10 +51040,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G550" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H550" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I550" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -51106,7 +51106,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC550" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD550" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -51132,10 +51132,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G551" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H551" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I551" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -51198,7 +51198,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC551" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD551" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -51209,25 +51209,25 @@
         <x:v>vision_config/layer_14</x:v>
       </x:c>
       <x:c r="B552" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C552" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D552" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E552" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F552" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G552" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H552" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I552" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -51290,10 +51290,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC552" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD552" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="553" ht="24" hidden="0" customHeight="1">
@@ -51316,10 +51316,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G553" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H553" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I553" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -51382,7 +51382,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC553" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD553" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -51408,10 +51408,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G554" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H554" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I554" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -51474,7 +51474,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC554" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD554" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -51500,10 +51500,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G555" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H555" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I555" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -51566,7 +51566,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC555" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD555" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -51592,10 +51592,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G556" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H556" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I556" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -51658,7 +51658,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC556" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD556" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -51684,10 +51684,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G557" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H557" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I557" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -51750,7 +51750,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC557" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD557" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -51776,10 +51776,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G558" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H558" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I558" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -51842,7 +51842,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC558" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD558" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -51868,10 +51868,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G559" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H559" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I559" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -51934,7 +51934,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC559" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD559" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -51960,10 +51960,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G560" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H560" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I560" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -52026,7 +52026,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC560" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD560" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -52052,10 +52052,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G561" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H561" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I561" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -52118,7 +52118,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC561" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD561" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -52144,10 +52144,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G562" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H562" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I562" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -52210,7 +52210,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC562" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD562" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -52236,10 +52236,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G563" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H563" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I563" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -52302,7 +52302,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC563" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD563" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -52328,10 +52328,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G564" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H564" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I564" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -52394,7 +52394,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC564" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD564" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -52405,25 +52405,25 @@
         <x:v>vision_config/layer_15</x:v>
       </x:c>
       <x:c r="B565" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C565" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D565" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E565" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F565" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G565" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H565" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I565" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -52486,10 +52486,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC565" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD565" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="566" ht="24" hidden="0" customHeight="1">
@@ -52512,10 +52512,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G566" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H566" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I566" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -52578,7 +52578,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC566" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD566" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -52604,10 +52604,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G567" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H567" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I567" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -52670,7 +52670,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC567" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD567" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -52696,10 +52696,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G568" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H568" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I568" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -52762,7 +52762,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC568" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD568" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -52788,10 +52788,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G569" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H569" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I569" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -52854,7 +52854,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC569" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD569" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -52880,10 +52880,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G570" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H570" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I570" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -52946,7 +52946,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC570" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD570" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -52972,10 +52972,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G571" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H571" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I571" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -53038,7 +53038,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC571" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD571" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -53064,10 +53064,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G572" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H572" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I572" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -53130,7 +53130,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC572" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD572" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -53156,10 +53156,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G573" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H573" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I573" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -53222,7 +53222,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC573" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD573" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -53248,10 +53248,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G574" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H574" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I574" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -53314,7 +53314,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC574" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD574" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -53340,10 +53340,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G575" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H575" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I575" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -53406,7 +53406,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC575" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD575" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -53432,10 +53432,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G576" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H576" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I576" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -53498,7 +53498,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC576" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD576" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -53524,10 +53524,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G577" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H577" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I577" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -53590,7 +53590,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC577" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD577" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -53601,25 +53601,25 @@
         <x:v>vision_config/layer_16</x:v>
       </x:c>
       <x:c r="B578" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C578" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D578" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E578" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F578" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G578" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H578" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I578" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -53682,10 +53682,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC578" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD578" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="579" ht="24" hidden="0" customHeight="1">
@@ -53708,10 +53708,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G579" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H579" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I579" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -53774,7 +53774,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC579" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD579" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -53800,10 +53800,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G580" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H580" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I580" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -53866,7 +53866,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC580" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD580" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -53892,10 +53892,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G581" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H581" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I581" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -53958,7 +53958,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC581" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD581" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -53984,10 +53984,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G582" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H582" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I582" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -54050,7 +54050,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC582" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD582" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -54076,10 +54076,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G583" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H583" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I583" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -54142,7 +54142,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC583" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD583" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -54168,10 +54168,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G584" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H584" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I584" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -54234,7 +54234,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC584" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD584" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -54260,10 +54260,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G585" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H585" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I585" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -54326,7 +54326,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC585" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD585" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -54352,10 +54352,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G586" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H586" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I586" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -54418,7 +54418,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC586" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD586" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -54444,10 +54444,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G587" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H587" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I587" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -54510,7 +54510,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC587" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD587" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -54536,10 +54536,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G588" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H588" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I588" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -54602,7 +54602,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC588" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD588" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -54628,10 +54628,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G589" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H589" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I589" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -54694,7 +54694,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC589" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD589" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -54720,10 +54720,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G590" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H590" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I590" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -54786,7 +54786,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC590" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD590" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -54797,25 +54797,25 @@
         <x:v>vision_config/layer_17</x:v>
       </x:c>
       <x:c r="B591" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C591" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D591" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E591" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F591" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G591" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H591" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I591" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -54878,10 +54878,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC591" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD591" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="592" ht="24" hidden="0" customHeight="1">
@@ -54904,10 +54904,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G592" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H592" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I592" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -54970,7 +54970,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC592" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD592" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -54996,10 +54996,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G593" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H593" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I593" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -55062,7 +55062,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC593" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD593" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -55088,10 +55088,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G594" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H594" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I594" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -55154,7 +55154,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC594" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD594" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -55180,10 +55180,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G595" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H595" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I595" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -55246,7 +55246,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC595" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD595" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -55272,10 +55272,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G596" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H596" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I596" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -55338,7 +55338,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC596" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD596" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -55364,10 +55364,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G597" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H597" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I597" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -55430,7 +55430,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC597" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD597" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -55456,10 +55456,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G598" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H598" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I598" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -55522,7 +55522,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC598" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD598" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -55548,10 +55548,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G599" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H599" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I599" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -55614,7 +55614,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC599" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD599" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -55640,10 +55640,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G600" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H600" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I600" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -55706,7 +55706,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC600" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD600" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -55732,10 +55732,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G601" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H601" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I601" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -55798,7 +55798,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC601" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD601" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -55824,10 +55824,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G602" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H602" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I602" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -55890,7 +55890,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC602" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD602" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -55916,10 +55916,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G603" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H603" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I603" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -55982,7 +55982,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC603" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD603" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -55993,25 +55993,25 @@
         <x:v>vision_config/layer_18</x:v>
       </x:c>
       <x:c r="B604" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C604" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D604" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E604" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F604" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G604" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H604" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I604" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -56074,10 +56074,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC604" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD604" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="605" ht="24" hidden="0" customHeight="1">
@@ -56100,10 +56100,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G605" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H605" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I605" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -56166,7 +56166,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC605" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD605" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -56192,10 +56192,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G606" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H606" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I606" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -56258,7 +56258,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC606" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD606" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -56284,10 +56284,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G607" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H607" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I607" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -56350,7 +56350,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC607" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD607" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -56376,10 +56376,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G608" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H608" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I608" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -56442,7 +56442,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC608" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD608" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -56468,10 +56468,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G609" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H609" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I609" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -56534,7 +56534,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC609" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD609" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -56560,10 +56560,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G610" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H610" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I610" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -56626,7 +56626,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC610" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD610" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -56652,10 +56652,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G611" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H611" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I611" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -56718,7 +56718,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC611" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD611" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -56744,10 +56744,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G612" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H612" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I612" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -56810,7 +56810,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC612" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD612" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -56836,10 +56836,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G613" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H613" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I613" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -56902,7 +56902,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC613" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD613" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -56928,10 +56928,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G614" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H614" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I614" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -56994,7 +56994,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC614" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD614" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -57020,10 +57020,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G615" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H615" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I615" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -57086,7 +57086,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC615" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD615" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -57112,10 +57112,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G616" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H616" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I616" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -57178,7 +57178,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC616" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD616" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -57189,25 +57189,25 @@
         <x:v>vision_config/layer_19</x:v>
       </x:c>
       <x:c r="B617" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C617" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D617" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E617" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F617" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G617" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H617" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I617" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -57270,10 +57270,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC617" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD617" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="618" ht="24" hidden="0" customHeight="1">
@@ -57296,10 +57296,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G618" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H618" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I618" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -57362,7 +57362,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC618" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD618" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -57388,10 +57388,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G619" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H619" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I619" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -57454,7 +57454,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC619" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD619" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -57480,10 +57480,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G620" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H620" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I620" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -57546,7 +57546,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC620" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD620" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -57572,10 +57572,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G621" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H621" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I621" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -57638,7 +57638,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC621" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD621" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -57664,10 +57664,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G622" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H622" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I622" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -57730,7 +57730,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC622" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD622" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -57756,10 +57756,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G623" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H623" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I623" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -57822,7 +57822,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC623" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD623" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -57848,10 +57848,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G624" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H624" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I624" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -57914,7 +57914,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC624" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD624" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -57940,10 +57940,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G625" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H625" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I625" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -58006,7 +58006,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC625" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD625" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -58032,10 +58032,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G626" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H626" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I626" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -58098,7 +58098,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC626" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD626" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -58124,10 +58124,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G627" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H627" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I627" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -58190,7 +58190,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC627" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD627" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -58216,10 +58216,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G628" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H628" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I628" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -58282,7 +58282,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC628" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD628" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -58308,10 +58308,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G629" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H629" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I629" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -58374,7 +58374,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC629" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD629" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -58385,25 +58385,25 @@
         <x:v>vision_config/layer_20</x:v>
       </x:c>
       <x:c r="B630" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C630" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D630" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E630" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F630" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G630" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H630" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I630" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -58466,10 +58466,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC630" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD630" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="631" ht="24" hidden="0" customHeight="1">
@@ -58492,10 +58492,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G631" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H631" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I631" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -58558,7 +58558,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC631" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD631" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -58584,10 +58584,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G632" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H632" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I632" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -58650,7 +58650,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC632" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD632" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -58676,10 +58676,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G633" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H633" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I633" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -58742,7 +58742,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC633" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD633" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -58768,10 +58768,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G634" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H634" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I634" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -58834,7 +58834,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC634" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD634" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -58860,10 +58860,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G635" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H635" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I635" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -58926,7 +58926,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC635" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD635" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -58952,10 +58952,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G636" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H636" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I636" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -59018,7 +59018,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC636" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD636" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -59044,10 +59044,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G637" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H637" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I637" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -59110,7 +59110,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC637" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD637" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -59136,10 +59136,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G638" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H638" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I638" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -59202,7 +59202,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC638" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD638" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -59228,10 +59228,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G639" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H639" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I639" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -59294,7 +59294,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC639" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD639" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -59320,10 +59320,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G640" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H640" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I640" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -59386,7 +59386,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC640" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD640" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -59412,10 +59412,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G641" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H641" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I641" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -59478,7 +59478,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC641" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD641" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -59504,10 +59504,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G642" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H642" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I642" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -59570,7 +59570,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC642" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD642" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -59581,25 +59581,25 @@
         <x:v>vision_config/layer_21</x:v>
       </x:c>
       <x:c r="B643" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C643" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D643" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E643" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F643" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G643" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H643" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I643" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -59662,10 +59662,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC643" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD643" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="644" ht="24" hidden="0" customHeight="1">
@@ -59688,10 +59688,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G644" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H644" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I644" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -59754,7 +59754,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC644" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD644" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -59780,10 +59780,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G645" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H645" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I645" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -59846,7 +59846,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC645" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD645" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -59872,10 +59872,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G646" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H646" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I646" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -59938,7 +59938,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC646" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD646" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -59964,10 +59964,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G647" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H647" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I647" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -60030,7 +60030,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC647" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD647" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -60056,10 +60056,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G648" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H648" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I648" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -60122,7 +60122,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC648" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD648" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -60148,10 +60148,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G649" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H649" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I649" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -60214,7 +60214,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC649" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD649" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -60240,10 +60240,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G650" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H650" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I650" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -60306,7 +60306,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC650" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD650" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -60332,10 +60332,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G651" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H651" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I651" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -60398,7 +60398,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC651" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD651" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -60424,10 +60424,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G652" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H652" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I652" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -60490,7 +60490,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC652" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD652" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -60516,10 +60516,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G653" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H653" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I653" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -60582,7 +60582,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC653" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD653" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -60608,10 +60608,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G654" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H654" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I654" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -60674,7 +60674,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC654" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD654" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -60700,10 +60700,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G655" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H655" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I655" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -60766,7 +60766,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC655" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD655" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -60777,25 +60777,25 @@
         <x:v>vision_config/layer_22</x:v>
       </x:c>
       <x:c r="B656" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C656" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D656" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E656" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F656" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G656" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H656" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I656" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -60858,10 +60858,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC656" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD656" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="657" ht="24" hidden="0" customHeight="1">
@@ -60884,10 +60884,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G657" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H657" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I657" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -60950,7 +60950,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC657" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD657" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -60976,10 +60976,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G658" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H658" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I658" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -61042,7 +61042,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC658" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD658" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -61068,10 +61068,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G659" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H659" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I659" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -61134,7 +61134,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC659" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD659" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -61160,10 +61160,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G660" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H660" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I660" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -61226,7 +61226,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC660" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD660" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -61252,10 +61252,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G661" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H661" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I661" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -61318,7 +61318,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC661" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD661" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -61344,10 +61344,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G662" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H662" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I662" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -61410,7 +61410,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC662" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD662" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -61436,10 +61436,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G663" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H663" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I663" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -61502,7 +61502,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC663" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD663" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -61528,10 +61528,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G664" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H664" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I664" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -61594,7 +61594,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC664" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD664" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -61620,10 +61620,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G665" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H665" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I665" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -61686,7 +61686,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC665" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD665" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -61712,10 +61712,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G666" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H666" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I666" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -61778,7 +61778,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC666" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD666" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -61804,10 +61804,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G667" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H667" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I667" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -61870,7 +61870,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC667" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD667" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -61896,10 +61896,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G668" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H668" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I668" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -61962,7 +61962,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC668" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD668" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -61973,25 +61973,25 @@
         <x:v>vision_config/layer_23</x:v>
       </x:c>
       <x:c r="B669" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C669" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D669" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E669" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F669" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G669" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H669" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I669" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -62054,10 +62054,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC669" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD669" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="670" ht="24" hidden="0" customHeight="1">
@@ -62080,10 +62080,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G670" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H670" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I670" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -62146,7 +62146,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC670" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD670" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -62172,10 +62172,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G671" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H671" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I671" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -62238,7 +62238,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC671" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD671" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -62264,10 +62264,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G672" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H672" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I672" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -62330,7 +62330,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC672" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD672" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -62356,10 +62356,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G673" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H673" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I673" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -62422,7 +62422,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC673" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD673" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -62448,10 +62448,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G674" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H674" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I674" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -62514,7 +62514,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC674" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD674" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -62540,10 +62540,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G675" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H675" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I675" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -62606,7 +62606,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC675" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD675" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -62632,10 +62632,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G676" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H676" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I676" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -62698,7 +62698,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC676" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD676" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -62724,10 +62724,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G677" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H677" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I677" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -62790,7 +62790,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC677" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD677" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -62816,10 +62816,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G678" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H678" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I678" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -62882,7 +62882,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC678" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD678" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -62908,10 +62908,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G679" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H679" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I679" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -62974,7 +62974,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC679" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD679" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -63000,10 +63000,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G680" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H680" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I680" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -63066,7 +63066,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC680" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD680" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -63092,10 +63092,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G681" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H681" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I681" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -63158,7 +63158,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC681" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD681" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -63169,25 +63169,25 @@
         <x:v>vision_config/layer_24</x:v>
       </x:c>
       <x:c r="B682" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C682" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D682" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E682" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F682" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G682" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H682" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I682" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -63250,10 +63250,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC682" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD682" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="683" ht="24" hidden="0" customHeight="1">
@@ -63276,10 +63276,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G683" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H683" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I683" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -63342,7 +63342,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC683" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD683" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -63368,10 +63368,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G684" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H684" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I684" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -63434,7 +63434,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC684" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD684" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -63460,10 +63460,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G685" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H685" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I685" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -63526,7 +63526,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC685" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD685" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -63552,10 +63552,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G686" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H686" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I686" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -63618,7 +63618,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC686" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD686" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -63644,10 +63644,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G687" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H687" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I687" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -63710,7 +63710,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC687" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD687" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -63736,10 +63736,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G688" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H688" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I688" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -63802,7 +63802,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC688" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD688" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -63828,10 +63828,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G689" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H689" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I689" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -63894,7 +63894,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC689" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD689" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -63920,10 +63920,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G690" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H690" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I690" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -63986,7 +63986,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC690" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD690" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -64012,10 +64012,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G691" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H691" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I691" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -64078,7 +64078,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC691" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD691" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -64104,10 +64104,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G692" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H692" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I692" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -64170,7 +64170,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC692" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD692" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -64196,10 +64196,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G693" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H693" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I693" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -64262,7 +64262,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC693" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD693" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -64288,10 +64288,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G694" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H694" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I694" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -64354,7 +64354,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC694" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD694" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -64365,25 +64365,25 @@
         <x:v>vision_config/layer_25</x:v>
       </x:c>
       <x:c r="B695" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C695" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D695" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E695" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F695" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G695" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H695" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I695" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -64446,10 +64446,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC695" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD695" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="696" ht="24" hidden="0" customHeight="1">
@@ -64472,10 +64472,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G696" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H696" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I696" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -64538,7 +64538,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC696" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD696" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -64564,10 +64564,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G697" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H697" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I697" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -64630,7 +64630,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC697" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD697" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -64656,10 +64656,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G698" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H698" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I698" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -64722,7 +64722,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC698" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD698" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -64748,10 +64748,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G699" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H699" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I699" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -64814,7 +64814,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC699" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD699" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -64840,10 +64840,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G700" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H700" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I700" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -64906,7 +64906,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC700" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD700" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -64932,10 +64932,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G701" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H701" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I701" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -64998,7 +64998,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC701" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD701" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -65024,10 +65024,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G702" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H702" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I702" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -65090,7 +65090,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC702" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD702" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -65116,10 +65116,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G703" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H703" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I703" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -65182,7 +65182,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC703" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD703" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -65208,10 +65208,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G704" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H704" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I704" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -65274,7 +65274,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC704" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD704" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -65300,10 +65300,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G705" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H705" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I705" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -65366,7 +65366,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC705" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD705" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -65392,10 +65392,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G706" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H706" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I706" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -65458,7 +65458,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC706" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD706" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -65484,10 +65484,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G707" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H707" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I707" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -65550,7 +65550,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC707" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；独立逻辑矩阵，不断言实际融合与存储</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；独立逻辑矩阵，不断言实际融合与存储</x:v>
       </x:c>
       <x:c r="AD707" s="12" t="str">
         <x:v>Y=X@W^T; width=heads*head_dim</x:v>
@@ -65561,25 +65561,25 @@
         <x:v>vision_config/layer_26</x:v>
       </x:c>
       <x:c r="B708" s="12" t="str">
-        <x:v>position_and_cache</x:v>
+        <x:v>position_and_layout</x:v>
       </x:c>
       <x:c r="C708" s="12" t="str">
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="D708" s="12" t="str">
-        <x:v>位置/缓存</x:v>
+        <x:v>位置/布局</x:v>
       </x:c>
       <x:c r="E708" s="12" t="str">
         <x:v>Q,K,V projected; B,L_img</x:v>
       </x:c>
       <x:c r="F708" s="12" t="str">
-        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_KV,72]</x:v>
+        <x:v>Q:[B,16,L_img,72]; K,V:[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G708" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H708" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I708" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -65642,10 +65642,10 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC708" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD708" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="709" ht="24" hidden="0" customHeight="1">
@@ -65668,10 +65668,10 @@
         <x:v>[B,16,L_img,72]</x:v>
       </x:c>
       <x:c r="G709" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H709" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I709" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -65734,7 +65734,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC709" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；稀疏选块/线性分支需按实现，不能据此声称稠密执行或峰值中间内存</x:v>
       </x:c>
       <x:c r="AD709" s="12" t="str">
         <x:v>softmax(QK^T / sqrt(head_dim) + mask)V（数学参考）</x:v>
@@ -65760,10 +65760,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G710" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H710" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I710" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -65826,7 +65826,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC710" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD710" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -65852,10 +65852,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G711" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H711" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I711" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -65918,7 +65918,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC711" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD711" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -65944,10 +65944,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G712" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H712" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I712" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -66010,7 +66010,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC712" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD712" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -66036,10 +66036,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G713" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H713" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I713" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -66102,7 +66102,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC713" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD713" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -66128,10 +66128,10 @@
         <x:v>[B,L_img,4304]</x:v>
       </x:c>
       <x:c r="G714" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H714" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I714" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -66194,7 +66194,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC714" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；是否额外gate矩阵与门控分支维度需要实现；不能仅由silu推定完整SwiGLU</x:v>
       </x:c>
       <x:c r="AD714" s="12" t="str">
         <x:v>config.hidden_act=未核验</x:v>
@@ -66220,10 +66220,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G715" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H715" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I715" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -66286,7 +66286,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC715" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD715" s="12" t="str">
         <x:v>Y=X@W^T</x:v>
@@ -66312,10 +66312,10 @@
         <x:v>[B,L_img,1152]</x:v>
       </x:c>
       <x:c r="G716" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_img；模态独立长度</x:v>
       </x:c>
       <x:c r="H716" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_img由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I716" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -66378,7 +66378,7 @@
         <x:v>https://huggingface.co/openbmb/AgentCPM-GUI/resolve/433b33feda9fed1e13b509cfd65d73f0a3fc4dff/config.json</x:v>
       </x:c>
       <x:c r="AC716" s="12" t="str">
-        <x:v>视觉编码/prefill，不随每个文本decode重复；</x:v>
+        <x:v>视觉编码，Q/K/V同L_img，无文本历史KV；</x:v>
       </x:c>
       <x:c r="AD716" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -66631,7 +66631,7 @@
         </x:is>
       </x:c>
       <x:c r="C7" s="28" t="n">
-        <x:f>IF(ISNUMBER(C6),IF(AND(C20&gt;=1,MOD(C6,C20)=0),C6/C20,"未核验"),"未核验")</x:f>
+        <x:f>IF(ISNUMBER(C20),IF(C20&gt;=1,IF(MOD(C20,1)=0,IF(ISNUMBER(C6),IF(MOD(C6,C20)=0,C6/C20,"未核验"),"未核验"),"未核验"),"未核验"),"未核验")</x:f>
         <x:v>28</x:v>
       </x:c>
       <x:c r="D7" s="28" t="str">
@@ -66895,7 +66895,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D20" s="28"/>
-      <x:c r="E20" s="28"/>
+      <x:c r="E20" s="28" t="str">
+        <x:f>IF(ISNUMBER(C20),IF(C20&gt;=1,IF(MOD(C20,1)=0,"正整数场景输入；实际支持未核验","须为正整数"),"须为正整数"),"须为正整数")</x:f>
+        <x:v>正整数场景输入；实际支持未核验</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="28" t="str">
@@ -66908,7 +66911,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D21" s="28"/>
-      <x:c r="E21" s="28"/>
+      <x:c r="E21" s="28" t="str">
+        <x:f>IF(ISNUMBER(C21),IF(C21&gt;=1,IF(MOD(C21,1)=0,"正整数场景输入；实际支持未核验","须为正整数"),"须为正整数"),"须为正整数")</x:f>
+        <x:v>正整数场景输入；实际支持未核验</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="28" t="str">
@@ -67615,8 +67621,8 @@
       <x:c r="E77" s="28"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
-    <x:dataValidation type="whole" operator="between" sqref="C3:C4">
+  <x:dataValidations count="3">
+    <x:dataValidation type="whole" operator="between" sqref="C3">
       <x:formula1>1</x:formula1>
       <x:formula2>16</x:formula2>
     </x:dataValidation>
@@ -67624,6 +67630,9 @@
       <x:formula1>1</x:formula1>
       <x:formula2>8</x:formula2>
     </x:dataValidation>
+    <x:dataValidation type="whole" operator="greaterThanOrEqual" sqref="C20:C21">
+      <x:formula1>1</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
